--- a/data/trans_bre/PCS12_SP_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/PCS12_SP_R2-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12)</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,47; 20,11</t>
+          <t>9,12; 19,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 13,65</t>
+          <t>2,68; 13,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 13,44</t>
+          <t>2,75; 13,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 8,97</t>
+          <t>-2,22; 9,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,92; 50,88</t>
+          <t>19,84; 49,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,47; 32,76</t>
+          <t>5,65; 31,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,29; 33,76</t>
+          <t>5,5; 33,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 18,66</t>
+          <t>-4,17; 20,29</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,13; 25,31</t>
+          <t>16,06; 25,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,82; 15,46</t>
+          <t>6,73; 15,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,61; 14,72</t>
+          <t>5,66; 14,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-23,12; 14,71</t>
+          <t>-23,38; 14,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,19; 68,06</t>
+          <t>38,04; 69,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,55; 37,38</t>
+          <t>14,46; 37,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,99; 42,74</t>
+          <t>14,61; 42,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,64; 40,55</t>
+          <t>-31,82; 40,18</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,67; 15,76</t>
+          <t>4,49; 15,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,33; 17,13</t>
+          <t>6,35; 17,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 13,12</t>
+          <t>3,38; 13,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 38,4</t>
+          <t>3,15; 37,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,86; 36,49</t>
+          <t>9,28; 36,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,25; 45,37</t>
+          <t>14,55; 45,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,05; 34,22</t>
+          <t>7,9; 35,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,81; 94,06</t>
+          <t>6,95; 90,17</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,98; 15,94</t>
+          <t>6,96; 15,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,18; 14,05</t>
+          <t>5,11; 14,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,06; 12,83</t>
+          <t>3,98; 12,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 5,92</t>
+          <t>-9,83; 6,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,18; 39,72</t>
+          <t>15,55; 39,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,89; 32,87</t>
+          <t>10,47; 33,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,38; 37,07</t>
+          <t>10,15; 36,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-19,23; 11,53</t>
+          <t>-17,74; 12,77</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,98; 16,81</t>
+          <t>11,92; 16,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,77; 12,92</t>
+          <t>7,89; 12,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,09; 11,13</t>
+          <t>6,49; 11,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 12,41</t>
+          <t>-5,72; 12,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,35; 40,73</t>
+          <t>27,33; 41,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,15; 30,35</t>
+          <t>17,5; 30,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,88; 29,5</t>
+          <t>16,09; 29,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 25,91</t>
+          <t>-11,39; 26,23</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/PCS12_SP_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/PCS12_SP_R2-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>2,97</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,12; 19,77</t>
+          <t>9,13; 20,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,68; 13,67</t>
+          <t>2,89; 13,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,75; 13,76</t>
+          <t>2,54; 13,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 9,79</t>
+          <t>-2,33; 7,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,84; 49,42</t>
+          <t>20,4; 50,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,65; 31,94</t>
+          <t>6,14; 32,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,5; 33,72</t>
+          <t>5,58; 33,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 20,29</t>
+          <t>-4,32; 16,97</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>13,04</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>35,38%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,06; 25,42</t>
+          <t>15,96; 24,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,73; 15,54</t>
+          <t>6,7; 15,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,66; 14,31</t>
+          <t>5,18; 14,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-23,38; 14,51</t>
+          <t>8,62; 17,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,04; 69,88</t>
+          <t>38,14; 67,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,46; 37,25</t>
+          <t>14,44; 37,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,61; 42,18</t>
+          <t>13,26; 40,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,82; 40,18</t>
+          <t>21,66; 50,2</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16,2</t>
+          <t>6,52</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,49; 15,47</t>
+          <t>3,91; 15,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,35; 17,2</t>
+          <t>6,25; 17,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 13,26</t>
+          <t>3,82; 14,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 37,43</t>
+          <t>1,58; 11,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,28; 36,18</t>
+          <t>7,53; 35,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,55; 45,86</t>
+          <t>14,53; 46,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,9; 35,59</t>
+          <t>8,95; 37,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,95; 90,17</t>
+          <t>3,21; 26,51</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>5,06</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,96; 15,81</t>
+          <t>7,0; 15,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,11; 14,16</t>
+          <t>5,26; 14,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,98; 12,71</t>
+          <t>4,46; 12,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 6,56</t>
+          <t>0,68; 9,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,55; 39,28</t>
+          <t>15,78; 39,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,47; 33,04</t>
+          <t>11,02; 34,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,15; 36,84</t>
+          <t>11,46; 37,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,74; 12,77</t>
+          <t>1,31; 19,36</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,92</t>
+          <t>7,46</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,92; 16,96</t>
+          <t>12,04; 16,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,89; 12,75</t>
+          <t>7,93; 12,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,49; 11,25</t>
+          <t>6,31; 11,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 12,23</t>
+          <t>5,03; 10,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,33; 41,75</t>
+          <t>27,23; 41,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,5; 30,03</t>
+          <t>17,39; 29,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,09; 29,91</t>
+          <t>15,74; 29,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 26,23</t>
+          <t>10,88; 22,7</t>
         </is>
       </c>
     </row>
